--- a/data/trans_dic/P1401-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1401-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,37</t>
+          <t>0,25; 2,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,94</t>
+          <t>2,05; 4,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,39</t>
+          <t>0,6; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,63</t>
+          <t>1,17; 4,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,99</t>
+          <t>1,14; 3,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,71</t>
+          <t>0,27; 1,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,85</t>
+          <t>0,83; 2,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,49</t>
+          <t>1,83; 3,65</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,46</t>
+          <t>0,26; 2,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,11</t>
+          <t>0,19; 2,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,74</t>
+          <t>1,22; 3,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,79</t>
+          <t>0,59; 4,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,16</t>
+          <t>1,05; 3,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,53</t>
+          <t>0,63; 2,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,92</t>
+          <t>0,24; 1,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,9</t>
+          <t>1,37; 3,1</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,79</t>
+          <t>1,28; 3,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,62</t>
+          <t>0,53; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,4</t>
+          <t>1,54; 4,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,07</t>
+          <t>1,55; 6,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,04</t>
+          <t>1,88; 9,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,47</t>
+          <t>0,61; 3,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,93</t>
+          <t>1,48; 3,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,36</t>
+          <t>1,14; 3,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,99</t>
+          <t>1,53; 3,63</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,23</t>
+          <t>0,69; 2,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,27</t>
+          <t>0,3; 1,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,95</t>
+          <t>1,25; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,43</t>
+          <t>0,96; 3,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,54</t>
+          <t>1,29; 3,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,32</t>
+          <t>1,35; 2,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,29</t>
+          <t>1,02; 2,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,92</t>
+          <t>0,86; 1,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,27</t>
+          <t>1,45; 2,44</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,91</t>
+          <t>0,19; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,69</t>
+          <t>0,74; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,74</t>
+          <t>0,69; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,84</t>
+          <t>1,43; 3,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,15</t>
+          <t>1,69; 4,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,99</t>
+          <t>2,37; 4,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,66</t>
+          <t>1,14; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,99</t>
+          <t>1,45; 3,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,15</t>
+          <t>1,82; 3,13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,71</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1243,32 +1243,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,69</t>
+          <t>1,08; 2,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,99</t>
+          <t>0,63; 2,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,39</t>
+          <t>1,67; 3,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,29</t>
+          <t>0,88; 2,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,69</t>
+          <t>0,49; 1,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,49</t>
+          <t>1,27; 2,54</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,61</t>
+          <t>0,8; 1,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,2</t>
+          <t>0,6; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,41</t>
+          <t>1,62; 2,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,58</t>
+          <t>1,58; 2,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,57</t>
+          <t>1,53; 2,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,52</t>
+          <t>1,92; 2,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,92</t>
+          <t>1,3; 1,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,79</t>
+          <t>1,17; 1,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,38</t>
+          <t>1,9; 2,47</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>17588</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>27037</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 5301</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>968; 10169</t>
+          <t>1065; 9875</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9806; 24933</t>
+          <t>11298; 26400</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1884; 10662</t>
+          <t>1889; 10516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4199; 16071</t>
+          <t>4075; 15290</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4567; 13384</t>
+          <t>5554; 15523</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2794; 12840</t>
+          <t>2028; 13570</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7050; 22135</t>
+          <t>6438; 21983</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17018; 33283</t>
+          <t>18976; 37900</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>18719</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1059; 10317</t>
+          <t>1079; 10064</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>735; 7944</t>
+          <t>729; 7700</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5473; 16883</t>
+          <t>5902; 18486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2118; 12796</t>
+          <t>1989; 14160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 10679</t>
+          <t>0; 11545</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3844; 12045</t>
+          <t>4432; 12894</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5126; 19170</t>
+          <t>4762; 18934</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1962; 14383</t>
+          <t>1828; 13829</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10872; 24126</t>
+          <t>12344; 28069</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2973</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>15474</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8033; 23825</t>
+          <t>8072; 24174</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2596; 13693</t>
+          <t>2791; 14053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3044; 22640</t>
+          <t>7243; 20498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3970; 15797</t>
+          <t>4034; 16481</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3142; 15017</t>
+          <t>3123; 15541</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1138; 5794</t>
+          <t>1150; 6149</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15406; 34961</t>
+          <t>13188; 33041</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7975; 23103</t>
+          <t>7869; 24557</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5618; 24877</t>
+          <t>10072; 23881</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>21116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>16218</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35129</t>
+          <t>37334</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8395; 25881</t>
+          <t>8001; 25232</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3636; 14599</t>
+          <t>3454; 14468</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13612; 30450</t>
+          <t>14095; 31740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6874; 26212</t>
+          <t>7370; 26930</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10915; 29215</t>
+          <t>10621; 28841</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7385; 22689</t>
+          <t>11635; 22737</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19482; 44025</t>
+          <t>19528; 45383</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>16465; 37953</t>
+          <t>16970; 37917</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23273; 45594</t>
+          <t>28926; 48600</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7227</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24876</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>32103</t>
+          <t>34171</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>946; 9731</t>
+          <t>946; 8948</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4860; 16672</t>
+          <t>4574; 15795</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3751; 12986</t>
+          <t>3918; 14131</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11697; 29180</t>
+          <t>10846; 28432</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11907; 30619</t>
+          <t>12471; 31657</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17152; 33449</t>
+          <t>19636; 36134</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14042; 33777</t>
+          <t>14485; 34070</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19578; 40652</t>
+          <t>19715; 42544</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23132; 41347</t>
+          <t>25345; 43668</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18455</t>
+          <t>19836</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4563</t>
+          <t>0; 5352</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2469,32 +2469,32 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11118; 29890</t>
+          <t>11970; 29503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7517; 21483</t>
+          <t>6768; 21968</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13091; 25816</t>
+          <t>14121; 27477</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12722; 31546</t>
+          <t>12098; 31602</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>7358; 23155</t>
+          <t>6707; 22022</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13065; 24901</t>
+          <t>13771; 27415</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64898</t>
+          <t>69788</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76049</t>
+          <t>82783</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>140947</t>
+          <t>152571</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>28280; 55190</t>
+          <t>27271; 53704</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20183; 40587</t>
+          <t>20328; 41949</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>47014; 81276</t>
+          <t>55776; 87710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54783; 91632</t>
+          <t>56020; 89759</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>54828; 90602</t>
+          <t>54167; 89208</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>60200; 90100</t>
+          <t>69768; 96504</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>91400; 133950</t>
+          <t>90470; 137533</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>82930; 123885</t>
+          <t>81175; 124248</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>118275; 165491</t>
+          <t>134038; 174368</t>
         </is>
       </c>
     </row>
